--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.64236749978031</v>
+        <v>9.204384718714302</v>
       </c>
       <c r="D2" t="n">
-        <v>57.55233854947591</v>
+        <v>9.352255014289835</v>
       </c>
       <c r="E2" t="n">
-        <v>17.0830607797865</v>
+        <v>2.775997376715306</v>
       </c>
       <c r="F2" t="n">
-        <v>17.35233797945317</v>
+        <v>2.81975492166114</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.65694283859794</v>
+        <v>4.331753211272165</v>
       </c>
       <c r="D3" t="n">
-        <v>26.43710975801515</v>
+        <v>4.296030335677462</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0830607797865</v>
+        <v>2.775997376715306</v>
       </c>
       <c r="F3" t="n">
-        <v>17.35233797945317</v>
+        <v>2.81975492166114</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>73.88434629313838</v>
+        <v>12.00620627263499</v>
       </c>
       <c r="D4" t="n">
-        <v>74.16906139436978</v>
+        <v>12.05247247658509</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0830607797865</v>
+        <v>2.775997376715306</v>
       </c>
       <c r="F4" t="n">
-        <v>17.35233797945317</v>
+        <v>2.81975492166114</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.61595471089779</v>
+        <v>7.575092640520891</v>
       </c>
       <c r="D5" t="n">
-        <v>46.3727997195714</v>
+        <v>7.535579954430352</v>
       </c>
       <c r="E5" t="n">
-        <v>17.0830607797865</v>
+        <v>2.775997376715306</v>
       </c>
       <c r="F5" t="n">
-        <v>17.35233797945317</v>
+        <v>2.81975492166114</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
